--- a/output/demo_generated_boq.xlsx
+++ b/output/demo_generated_boq.xlsx
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>33.53</v>
+        <v>12.08</v>
       </c>
       <c r="G2" t="n">
         <v>5200</v>
       </c>
       <c r="H2" t="n">
-        <v>174376.8</v>
+        <v>62790</v>
       </c>
     </row>
     <row r="3">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>145.8</v>
+        <v>52.5</v>
       </c>
       <c r="G3" t="n">
         <v>220</v>
       </c>
       <c r="H3" t="n">
-        <v>32076</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="4">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>146.93</v>
+        <v>19.04</v>
       </c>
       <c r="G4" t="n">
         <v>950</v>
       </c>
       <c r="H4" t="n">
-        <v>139583.5</v>
+        <v>18088</v>
       </c>
     </row>
     <row r="5">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>145.8</v>
+        <v>52.5</v>
       </c>
       <c r="G5" t="n">
         <v>120</v>
       </c>
       <c r="H5" t="n">
-        <v>17496</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="6">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>35.08</v>
+        <v>12.64</v>
       </c>
       <c r="G6" t="n">
         <v>5200</v>
       </c>
       <c r="H6" t="n">
-        <v>182413.92</v>
+        <v>65732.16</v>
       </c>
     </row>
     <row r="7">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>152.52</v>
+        <v>54.96</v>
       </c>
       <c r="G7" t="n">
         <v>220</v>
       </c>
       <c r="H7" t="n">
-        <v>33554.4</v>
+        <v>12091.2</v>
       </c>
     </row>
     <row r="8">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>159.61</v>
+        <v>20.69</v>
       </c>
       <c r="G8" t="n">
         <v>950</v>
       </c>
       <c r="H8" t="n">
-        <v>151629.5</v>
+        <v>19655.5</v>
       </c>
     </row>
     <row r="9">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>152.52</v>
+        <v>54.96</v>
       </c>
       <c r="G9" t="n">
         <v>120</v>
       </c>
       <c r="H9" t="n">
-        <v>18302.4</v>
+        <v>6595.2</v>
       </c>
     </row>
     <row r="10">
@@ -739,7 +739,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>749432.52</v>
+        <v>202802.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/demo_generated_boq.xlsx
+++ b/output/demo_generated_boq.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed measurements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abstract of quantities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priced BOQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deficiencies" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measurement Notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,17 +34,45 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0010264A"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010264A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE8E6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +80,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,48 +459,1622 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>TENDER BILL OF QUANTITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Demo bungalow</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Source file</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sample_floor_plan.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Measurement standard</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IS 1200 (building works) mapped to project CPWD-style item codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Scale method</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ifc_units</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>metres (IFC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>IFC units confirmed</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>QS name</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Demo QS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>QS sign-off</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Generated (UTC)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Measurement lines</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Priced total (INR)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>112725.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Deficiencies</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Assumptions and limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quantities come only from traced or IFC MeasuredElements. Auto-detected rectangles are an assist, not a tender source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Shared walls are measured once for brickwork. Internal plaster uses one or two faces from host spaces / shared flag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openings larger than 0.1 sqm are deducted from masonry and plaster (IS 1200). Smaller openings are not deducted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Wall height and thickness, slab/beam/column sizes, and excavation depth are never invented. Missing values appear on Deficiencies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Earthwork requires an excavation plan and depth or reduced levels — not a furniture floor plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rates are from the project knowledge_base CSV, not a live official CPWD DSR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>This workbook assists a quantity surveyor. The signed QS remains the tender authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MEP (electrical/plumbing points) is not auto-measured and must be entered as provisional/manual items.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Total Item Codes</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Priced Items</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Provisional Items</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Lines</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Deficiencies Recorded</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Total Estimated Cost (INR)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>112725.14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed Cost (INR)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>112725.14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Provisional Cost (INR)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Cost by Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Amount (INR)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Concrete</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>35531.9</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>31.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Flooring</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>24225</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Masonry</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>23738</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Doors_Windows</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>14548</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Finishing</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9009</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4833</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Earthwork</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>840.24</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>element_id</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>item_code</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>IS1200_note</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Vitrified tile flooring</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IS 1200 flooring: net space polygon area</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Living</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vitrified tile flooring</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>IS 1200 flooring: net space polygon area</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Brickwork in CM 1:6 in superstructure</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.391</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>IS 1200 brickwork LxHxT with 5.0% wastage; deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>M0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12mm cement plaster internal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>IS 1200 internal plaster 12mm, 1 face(s); deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>M0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Painting with acrylic emulsion (2 coats)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Internal paint on plastered faces; deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>M0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20mm cement plaster external</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>IS 1200 external plaster 20mm; deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Weatherproof exterior paint</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>External paint; deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>M0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>w-shared</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Party wall</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Brickwork in CM 1:6 in superstructure</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.174</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>IS 1200 brickwork LxHxT with 5.0% wastage; shared wall measured once. win1 1.440 sqm &lt;= 2.0 sqm not deducted (IS 1200 small opening)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>M0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>w-shared</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Party wall</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12mm cement plaster internal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I10" t="n">
+        <v>18</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>IS 1200 internal plaster 12mm, 2 face(s); shared wall measured once. win1 1.440 sqm &lt;= 2.0 sqm not deducted (IS 1200 small opening)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>M0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>w-shared</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Party wall</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Painting with acrylic emulsion (2 coats)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Internal paint on plastered faces; shared wall measured once. win1 1.440 sqm &lt;= 2.0 sqm not deducted (IS 1200 small opening)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>M0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>o1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bedroom door</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Flush door with frame</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Door counted from opening schedule (not guessed)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>M0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>win1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Living window</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aluminium sliding window</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Window area from opening schedule</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ft1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RCC M20 in foundation/footing</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>RCC footing LxBxD with 3.0% wastage (IS 1200)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>col1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RCC M20 in columns</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>RCC column with 3.0% wastage (IS 1200)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>M0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>bm1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RCC M20 in beams</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>RCC beam LxBxD with 3.0% wastage (IS 1200)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>M0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sl1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GF slab</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RCC M20 in slabs</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.283</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>RCC slab area x depth with 3.0% wastage (IS 1200)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ex1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Foundation excavation</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Earthwork excavation in foundation trenches</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Earthwork plan area x depth/RL difference (IS 1200); sections required for tender</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>M0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ex1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Foundation excavation</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Backfilling with excavated earth</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.052</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Backfill = excavation - footing volume (0.648 cum structure)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
           <t>sr_no</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>room</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>item_code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rate_inr</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>amount_inr</t>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>provisional</t>
         </is>
       </c>
     </row>
@@ -474,272 +2082,1846 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Room_1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3.1</v>
+      <c r="B2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Earthwork excavation in foundation trenches</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Brickwork in CM 1:6 in superstructure</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>cum</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5200</v>
-      </c>
-      <c r="H2" t="n">
-        <v>62790</v>
+      <c r="E2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Room_1</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>4.1</v>
+      <c r="B3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Backfilling with excavated earth</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12mm cement plaster internal</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>220</v>
-      </c>
-      <c r="H3" t="n">
-        <v>11550</v>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2.052</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Room_1</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5.1</v>
+      <c r="B4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RCC M20 in foundation/footing</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vitrified tile flooring</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="G4" t="n">
-        <v>950</v>
-      </c>
-      <c r="H4" t="n">
-        <v>18088</v>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Room_1</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>6.1</v>
+      <c r="B5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RCC M20 in columns</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Painting with acrylic emulsion (2 coats)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>120</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6300</v>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Room_2</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3.1</v>
+      <c r="B6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RCC M20 in beams</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Brickwork in CM 1:6 in superstructure</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
           <t>cum</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5200</v>
-      </c>
-      <c r="H6" t="n">
-        <v>65732.16</v>
+      <c r="E6" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Room_2</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.1</v>
+      <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RCC M20 in slabs</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12mm cement plaster internal</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>54.96</v>
-      </c>
-      <c r="G7" t="n">
-        <v>220</v>
-      </c>
-      <c r="H7" t="n">
-        <v>12091.2</v>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3.283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Room_2</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5.1</v>
+      <c r="B8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brickwork in CM 1:6 in superstructure</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vitrified tile flooring</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G8" t="n">
-        <v>950</v>
-      </c>
-      <c r="H8" t="n">
-        <v>19655.5</v>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4.565</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
+      <c r="B9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12mm cement plaster internal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20mm cement plaster external</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vitrified tile flooring</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Painting with acrylic emulsion (2 coats)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Weatherproof exterior paint</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Flush door with frame</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Aluminium sliding window</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>sr_no</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>item_code</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>rate_inr</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>amount_inr</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Earthwork excavation in foundation trenches</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>220</v>
+      </c>
+      <c r="G2" t="n">
+        <v>594</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Backfilling with excavated earth</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2.052</v>
+      </c>
+      <c r="F3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" t="n">
+        <v>246.24</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RCC M20 in foundation/footing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4535.6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RCC M20 in columns</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2001.6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RCC M20 in beams</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6342</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RCC M20 in slabs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3.283</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6900</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22652.7</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brickwork in CM 1:6 in superstructure</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4.565</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23738</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12mm cement plaster internal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>220</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6138</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20mm cement plaster external</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>290</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2871</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vitrified tile flooring</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>950</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24225</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Painting with acrylic emulsion (2 coats)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>120</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3348</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Weatherproof exterior paint</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>150</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1485</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Flush door with frame</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Aluminium sliding window</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6048</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL (priced items only)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n">
+        <v>112725.14</v>
+      </c>
+      <c r="H16" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>item_count</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>total_quantity</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>total_amount_inr</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>avg_rate</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>provisional_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Concrete</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.134</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35531.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6920.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Doors_Windows</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14548</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5962.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Earthwork</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.752</v>
+      </c>
+      <c r="D4" t="n">
+        <v>840.24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>176.82</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Finishing</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9009</v>
+      </c>
+      <c r="E5" t="n">
+        <v>238.33</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Flooring</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24225</v>
+      </c>
+      <c r="E6" t="n">
+        <v>950</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Masonry</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.565</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23738</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4833</v>
+      </c>
+      <c r="E8" t="n">
+        <v>127.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>element_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>w-dup</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate of wall w-shared; brickwork measured once (shared wall).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ex-bad</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Excavation depth missing (enter depth or top/bottom RL). Floor-plan height is not used.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>element_id</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>is1200_note</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>IS 1200 flooring: net space polygon area</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Living</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IS 1200 flooring: net space polygon area</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IS 1200 brickwork LxHxT with 5.0% wastage; deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2.391</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>M0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IS 1200 internal plaster 12mm, 1 face(s); deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>M0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Internal paint on plastered faces; deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>M0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IS 1200 external plaster 20mm; deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>w-ext-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bedroom north</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>External paint; deduct o1 2.100 sqm (IS 1200 compliant)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>M0008</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Room_2</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6.1</v>
+          <t>w-shared</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Party wall</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Painting with acrylic emulsion (2 coats)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+          <t>IS 1200 brickwork LxHxT with 5.0% wastage; shared wall measured once. win1 1.440 sqm &lt;= 2.0 sqm not deducted (IS 1200 small opening)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2.174</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>M0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>w-shared</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Party wall</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IS 1200 internal plaster 12mm, 2 face(s); shared wall measured once. win1 1.440 sqm &lt;= 2.0 sqm not deducted (IS 1200 small opening)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>sqm</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>54.96</v>
-      </c>
-      <c r="G9" t="n">
-        <v>120</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6595.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TOTAL ESTIMATED COST</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>202802.06</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>M0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>w-shared</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Party wall</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Internal paint on plastered faces; shared wall measured once. win1 1.440 sqm &lt;= 2.0 sqm not deducted (IS 1200 small opening)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>M0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>o1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bedroom door</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Door counted from opening schedule (not guessed)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>M0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>win1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Living window</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Window area from opening schedule</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ft1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RCC footing LxBxD with 3.0% wastage (IS 1200)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>col1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RCC column with 3.0% wastage (IS 1200)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>M0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>bm1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RCC beam LxBxD with 3.0% wastage (IS 1200)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>M0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sl1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GF slab</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RCC slab area x depth with 3.0% wastage (IS 1200)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3.283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ex1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Foundation excavation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Earthwork plan area x depth/RL difference (IS 1200); sections required for tender</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>M0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ex1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Foundation excavation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Backfill = excavation - footing volume (0.648 cum structure)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.052</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
       </c>
     </row>
   </sheetData>
